--- a/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_3_weights.xlsx
+++ b/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_3_weights.xlsx
@@ -441,7 +441,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.04764663684722427</v>
+        <v>-0.04764663684722426</v>
       </c>
       <c r="B2" t="n">
         <v>0.5666317570972599</v>
@@ -502,7 +502,7 @@
         <v>0.3127944855059579</v>
       </c>
       <c r="C7" t="n">
-        <v>0.844268978875544</v>
+        <v>0.8442689788755439</v>
       </c>
     </row>
     <row r="8">
@@ -532,10 +532,10 @@
         <v>-0.9536219345306148</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.4561852740638285</v>
+        <v>-0.4561852740638284</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7146082155173505</v>
+        <v>0.7146082155173508</v>
       </c>
     </row>
     <row r="11">
